--- a/data/sars/pacific/tables/Pacific_1998_Appendix2.xlsx
+++ b/data/sars/pacific/tables/Pacific_1998_Appendix2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/pacific/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749EA248-A87B-6E4F-BA30-A7F493AE687A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DEC1F58-7832-574B-9071-C1B751DD4DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7720" yWindow="500" windowWidth="27300" windowHeight="18020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="71">
   <si>
     <t>California sea lion</t>
   </si>
@@ -227,6 +227,12 @@
   </si>
   <si>
     <t>Southern Resident Stock</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -678,14 +684,14 @@
     <col min="7" max="7" width="5.59765625" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.19921875" style="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.59765625" style="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.59765625" style="14" customWidth="1"/>
     <col min="11" max="11" width="7.59765625" style="14" bestFit="1" customWidth="1"/>
     <col min="12" max="14" width="24.19921875" style="2" customWidth="1"/>
     <col min="15" max="18" width="51.19921875" style="2" customWidth="1"/>
     <col min="19" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:13" ht="30" x14ac:dyDescent="0.15">
       <c r="A1" s="7" t="s">
         <v>25</v>
       </c>
@@ -713,7 +719,9 @@
       <c r="I1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="8"/>
+      <c r="J1" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="K1" s="9"/>
       <c r="L1" s="5"/>
       <c r="M1" s="1"/>
@@ -806,6 +814,9 @@
       <c r="I4" s="19">
         <v>17</v>
       </c>
+      <c r="J4" s="14" t="s">
+        <v>70</v>
+      </c>
       <c r="M4" s="3"/>
     </row>
     <row r="5" spans="1:13" ht="15" x14ac:dyDescent="0.15">
@@ -836,6 +847,9 @@
       <c r="I5" s="19">
         <v>36</v>
       </c>
+      <c r="J5" s="14" t="s">
+        <v>70</v>
+      </c>
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:13" ht="15" x14ac:dyDescent="0.15">
@@ -926,6 +940,9 @@
       <c r="I8" s="18">
         <v>0</v>
       </c>
+      <c r="J8" s="14" t="s">
+        <v>70</v>
+      </c>
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="1:13" ht="15" x14ac:dyDescent="0.15">
@@ -1046,6 +1063,9 @@
       <c r="I12" s="19">
         <v>17</v>
       </c>
+      <c r="J12" s="14" t="s">
+        <v>70</v>
+      </c>
       <c r="M12" s="3"/>
     </row>
     <row r="13" spans="1:13" ht="15" x14ac:dyDescent="0.15">
@@ -1076,6 +1096,9 @@
       <c r="I13" s="19">
         <v>16</v>
       </c>
+      <c r="J13" s="14" t="s">
+        <v>70</v>
+      </c>
       <c r="M13" s="3"/>
     </row>
     <row r="14" spans="1:13" ht="15" x14ac:dyDescent="0.15">
@@ -1487,6 +1510,9 @@
       <c r="I27" s="15" t="s">
         <v>14</v>
       </c>
+      <c r="J27" s="14" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="28" spans="1:13" ht="15" x14ac:dyDescent="0.15">
       <c r="A28" s="9" t="s">
@@ -1633,7 +1659,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10" ht="15" x14ac:dyDescent="0.15">
       <c r="A33" s="9" t="s">
         <v>17</v>
       </c>
@@ -1662,7 +1688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:10" ht="15" x14ac:dyDescent="0.15">
       <c r="A34" s="9" t="s">
         <v>18</v>
       </c>
@@ -1691,7 +1717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10" ht="15" x14ac:dyDescent="0.15">
       <c r="A35" s="9" t="s">
         <v>20</v>
       </c>
@@ -1720,7 +1746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10" ht="15" x14ac:dyDescent="0.15">
       <c r="A36" s="9" t="s">
         <v>21</v>
       </c>
@@ -1749,7 +1775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:10" ht="15" x14ac:dyDescent="0.15">
       <c r="A37" s="15" t="s">
         <v>22</v>
       </c>
@@ -1777,8 +1803,11 @@
       <c r="I37" s="18">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+      <c r="J37" s="14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="15" x14ac:dyDescent="0.15">
       <c r="A38" s="9" t="s">
         <v>52</v>
       </c>
@@ -1807,7 +1836,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:10" ht="15" x14ac:dyDescent="0.15">
       <c r="A39" s="9" t="s">
         <v>11</v>
       </c>
@@ -1836,7 +1865,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:10" ht="15" x14ac:dyDescent="0.15">
       <c r="A40" s="9" t="s">
         <v>38</v>
       </c>
@@ -1865,7 +1894,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:10" ht="15" x14ac:dyDescent="0.15">
       <c r="A41" s="9" t="s">
         <v>51</v>
       </c>
@@ -1894,7 +1923,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:10" ht="15" x14ac:dyDescent="0.15">
       <c r="A42" s="9" t="s">
         <v>23</v>
       </c>
@@ -1923,7 +1952,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:10" ht="15" x14ac:dyDescent="0.15">
       <c r="A43" s="9" t="s">
         <v>12</v>
       </c>
@@ -1952,7 +1981,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:10" ht="15" x14ac:dyDescent="0.15">
       <c r="A44" s="9" t="s">
         <v>48</v>
       </c>
@@ -1981,7 +2010,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:10" ht="15" x14ac:dyDescent="0.15">
       <c r="A45" s="9" t="s">
         <v>47</v>
       </c>
@@ -2010,7 +2039,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:10" ht="15" x14ac:dyDescent="0.15">
       <c r="A46" s="9" t="s">
         <v>24</v>
       </c>
@@ -2039,7 +2068,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:10" ht="15" x14ac:dyDescent="0.15">
       <c r="A47" s="9" t="s">
         <v>13</v>
       </c>
@@ -2068,7 +2097,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:10" ht="15" x14ac:dyDescent="0.15">
       <c r="A48" s="9" t="s">
         <v>50</v>
       </c>
